--- a/Parkour/SourseFiles/Info.xlsx
+++ b/Parkour/SourseFiles/Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krist\Zomboid\Workshop\Parkour\SourseFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{764BDEF9-5203-4809-A3CF-0623ED164F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C398A73-6869-4313-B08F-9B7B2516AA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="2385" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="645" yWindow="5385" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>2.533 sec / SpeedScale 1.50 × TimePc 0.95 ≈ 1.604 sec</t>
   </si>
@@ -79,6 +79,18 @@
       </rPr>
       <t xml:space="preserve">. </t>
     </r>
+  </si>
+  <si>
+    <t>добавить анимку на перелаз окна</t>
+  </si>
+  <si>
+    <t>Добавить анимку для высокого забора</t>
+  </si>
+  <si>
+    <t>Добавить Урон на волт через окно</t>
+  </si>
+  <si>
+    <t>Добавить анимку простого перелаза</t>
   </si>
 </sst>
 </file>
@@ -407,20 +419,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:B4"/>
+  <dimension ref="B2:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="51.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="2:2" ht="60">
+    <row r="3" spans="2:5">
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="60">
       <c r="B4" s="2" t="s">
         <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="E5" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Parkour/SourseFiles/Info.xlsx
+++ b/Parkour/SourseFiles/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krist\Zomboid\Workshop\Parkour\SourseFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C398A73-6869-4313-B08F-9B7B2516AA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6D2766-9D9C-4EDE-A811-B7BE8A4C4785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="645" yWindow="5385" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>2.533 sec / SpeedScale 1.50 × TimePc 0.95 ≈ 1.604 sec</t>
   </si>
@@ -92,12 +92,24 @@
   <si>
     <t>Добавить анимку простого перелаза</t>
   </si>
+  <si>
+    <t>Проверить нормально ли отрабатывает увеличенная стамина с болезнями HER</t>
+  </si>
+  <si>
+    <t>Добавить перекат после большого падения</t>
+  </si>
+  <si>
+    <t>Добавить возможность залазить на машины</t>
+  </si>
+  <si>
+    <t>Добавить обычный прыжок, который реально перепрыгивает через объекты</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,6 +121,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -139,6 +158,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -419,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E5"/>
+  <dimension ref="B2:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="51.7109375" customWidth="1"/>
@@ -429,7 +449,7 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -451,7 +471,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6" spans="2:5">
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Parkour/SourseFiles/Info.xlsx
+++ b/Parkour/SourseFiles/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krist\Zomboid\Workshop\Parkour\SourseFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6D2766-9D9C-4EDE-A811-B7BE8A4C4785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A3B780-D7AF-4C2C-AF19-6AF9D4C58407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="645" yWindow="5385" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>2.533 sec / SpeedScale 1.50 × TimePc 0.95 ≈ 1.604 sec</t>
   </si>
@@ -90,9 +90,6 @@
     <t>Добавить Урон на волт через окно</t>
   </si>
   <si>
-    <t>Добавить анимку простого перелаза</t>
-  </si>
-  <si>
     <t>Проверить нормально ли отрабатывает увеличенная стамина с болезнями HER</t>
   </si>
   <si>
@@ -103,13 +100,25 @@
   </si>
   <si>
     <t>Добавить обычный прыжок, который реально перепрыгивает через объекты</t>
+  </si>
+  <si>
+    <t>Добавить анимку простого перелаза забора</t>
+  </si>
+  <si>
+    <t>"-&gt;" есть баг при перепрыгивании с крыши на крышу</t>
+  </si>
+  <si>
+    <t>"-&gt;" подправить анимацию</t>
+  </si>
+  <si>
+    <t>ЕСЛИ СДЕЛАТЬ ПЕРЕКАТ С КРЫШИ ТО ЛОК ИНПУТА</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,7 +133,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFC000"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -150,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -159,6 +175,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,13 +456,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E11"/>
+  <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="51.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:13">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,42 +470,53 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:5">
+    <row r="3" spans="2:13">
       <c r="E3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="60">
+    <row r="4" spans="2:13" ht="60">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="E5" t="s">
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="E6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="E8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="E11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5">
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
-      <c r="E11" t="s">
-        <v>6</v>
+    <row r="13" spans="2:13">
+      <c r="E13" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Parkour/SourseFiles/Info.xlsx
+++ b/Parkour/SourseFiles/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krist\Zomboid\Workshop\Parkour\SourseFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A3B780-D7AF-4C2C-AF19-6AF9D4C58407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D72829E-853B-4189-BE57-57DA42A93DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="645" yWindow="5385" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>2.533 sec / SpeedScale 1.50 × TimePc 0.95 ≈ 1.604 sec</t>
   </si>
@@ -112,6 +112,18 @@
   </si>
   <si>
     <t>ЕСЛИ СДЕЛАТЬ ПЕРЕКАТ С КРЫШИ ТО ЛОК ИНПУТА</t>
+  </si>
+  <si>
+    <t>Посмотреть что можно сделать со спринтерами которые замедляют при перекате</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>добавить чтобы можно было доджить ближе к концу предыдущего доджа, то есть додж чейн</t>
+  </si>
+  <si>
+    <t>Добавить расход стамины на додж</t>
   </si>
 </sst>
 </file>
@@ -456,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M13"/>
+  <dimension ref="B2:M16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="51.7109375" customWidth="1"/>
@@ -497,6 +509,9 @@
       </c>
     </row>
     <row r="7" spans="2:13">
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
@@ -509,14 +524,29 @@
         <v>10</v>
       </c>
     </row>
+    <row r="10" spans="2:13">
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="11" spans="2:13">
       <c r="E11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="2:13">
-      <c r="E13" t="s">
+      <c r="E13" s="3" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="E16" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Parkour/SourseFiles/Info.xlsx
+++ b/Parkour/SourseFiles/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krist\Zomboid\Workshop\Parkour\SourseFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D72829E-853B-4189-BE57-57DA42A93DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791B7647-8462-4FA0-98F5-6621A3FEBFAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="645" yWindow="5385" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>2.533 sec / SpeedScale 1.50 × TimePc 0.95 ≈ 1.604 sec</t>
   </si>
@@ -125,6 +125,12 @@
   <si>
     <t>Добавить расход стамины на додж</t>
   </si>
+  <si>
+    <t>1done</t>
+  </si>
+  <si>
+    <t>High Fence Y=100</t>
+  </si>
 </sst>
 </file>
 
@@ -152,7 +158,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="5"/>
+      <color rgb="FF7030A0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -483,6 +489,9 @@
       </c>
     </row>
     <row r="3" spans="2:13">
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
       <c r="E3" t="s">
         <v>3</v>
       </c>
@@ -509,6 +518,9 @@
       </c>
     </row>
     <row r="7" spans="2:13">
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
@@ -517,10 +529,10 @@
       </c>
     </row>
     <row r="8" spans="2:13">
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -540,7 +552,7 @@
       </c>
     </row>
     <row r="15" spans="2:13">
-      <c r="E15" t="s">
+      <c r="E15" s="4" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Parkour/SourseFiles/Info.xlsx
+++ b/Parkour/SourseFiles/Info.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krist\Zomboid\Workshop\Parkour\SourseFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\Project Parkour\ProjectParkour\Parkour\SourseFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791B7647-8462-4FA0-98F5-6621A3FEBFAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F8BE9E-D603-4FC3-A363-C1D63D767EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="645" yWindow="5385" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>2.533 sec / SpeedScale 1.50 × TimePc 0.95 ≈ 1.604 sec</t>
   </si>
@@ -131,12 +131,39 @@
   <si>
     <t>High Fence Y=100</t>
   </si>
+  <si>
+    <t>В мультплеере можно только с места делать прыжок</t>
+  </si>
+  <si>
+    <t>Добавить xp перелаз высокого забора!!!</t>
+  </si>
+  <si>
+    <t>IGUI Perks Parkour</t>
+  </si>
+  <si>
+    <t>В мультиплеере не показывается прыжок обычный</t>
+  </si>
+  <si>
+    <t>В мультиплеере проигрывается wall run, но персонаж остается снизу</t>
+  </si>
+  <si>
+    <t>У себя на экране он двигается как надо</t>
+  </si>
+  <si>
+    <t>В мультиплеере не отображается анимация vault</t>
+  </si>
+  <si>
+    <t>В мультиплеере не отображается анимация windwow sprint</t>
+  </si>
+  <si>
+    <t>В общем похоже ни одна анимация не отображается</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +190,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -184,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -194,6 +228,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M16"/>
+  <dimension ref="B2:M18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="51.7109375" customWidth="1"/>
@@ -492,7 +527,7 @@
       <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -524,7 +559,7 @@
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -537,28 +572,63 @@
       </c>
     </row>
     <row r="10" spans="2:13">
-      <c r="E10" t="s">
+      <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:13">
-      <c r="E11" t="s">
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>5</v>
       </c>
     </row>
+    <row r="12" spans="2:13">
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="13" spans="2:13">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
       <c r="E13" s="3" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="14" spans="2:13">
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="15" spans="2:13">
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
       <c r="E15" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="2:13">
-      <c r="E16" t="s">
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
